--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-020_fast-moving-products/evidence/final_outputs/REQ-23_fast-moving-products/REQ-23-D01_fast_moving_products.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-020_fast-moving-products/evidence/final_outputs/REQ-23_fast-moving-products/REQ-23-D01_fast_moving_products.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="70" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Data sources</t>
@@ -579,7 +579,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Sales/units/orders: public.order_transaction (source_name, market_place='Germany'). Product Name: inv_products.title / listing_data.title by SKU. Category: latest non-null order_transaction.category_name per SKU (~74% coverage; rest 'Uncategorised'). Current Stock: location_wise_inv_stock, location='Germany'.</t>
+          <t>RAW mcp.ledsone DB (read-only). Sales/units/orders: order_management.orders + order_item_info, joined to sub_source/source for channel (Amazon=1/eBay=2/Shopify=3), market_place='10' (Germany), status='Completed'. Current Stock: inventory.products + inventory.local_inventory_current_stock_location_wise, warehouse_location='Germany'. Product Name &amp; Category are curated catalog labels carried by SKU (raw combo titles are placeholders; category has no per-SKU raw home).</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>4 - 7W</t>
+          <t>4-7W Constant Current LED Driver, 300mA IP20 Rated Constant Current LED Driver Transformer, Converts AC85-265V into DC12-26V, IP20 Constant Current DC Transformers</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -2343,7 +2343,7 @@
         <v>73</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>629.03</v>
+        <v>629.04</v>
       </c>
       <c r="I4" s="8" t="n">
         <v>22</v>
@@ -2455,7 +2455,7 @@
         <v>62</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>467.78</v>
+        <v>467.79</v>
       </c>
       <c r="I6" s="8" t="n">
         <v>15</v>
@@ -2567,7 +2567,7 @@
         <v>54</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>378.38</v>
+        <v>378.39</v>
       </c>
       <c r="I8" s="8" t="n">
         <v>12</v>
@@ -2623,7 +2623,7 @@
         <v>18</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>183.18</v>
+        <v>183.19</v>
       </c>
       <c r="I9" s="12" t="n">
         <v>11</v>
@@ -3071,7 +3071,7 @@
         <v>10</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>181.33</v>
+        <v>181.34</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>5</v>
@@ -3127,7 +3127,7 @@
         <v>11</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>175.31</v>
+        <v>175.3</v>
       </c>
       <c r="I18" s="8" t="n">
         <v>6</v>
@@ -3183,7 +3183,7 @@
         <v>10</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>148.95</v>
+        <v>148.92</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>1</v>
@@ -3295,7 +3295,7 @@
         <v>11</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>49.48</v>
+        <v>49.49</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>3</v>
@@ -3519,7 +3519,7 @@
         <v>8</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>116.88</v>
+        <v>116.91</v>
       </c>
       <c r="I25" s="16" t="n">
         <v>1</v>
@@ -3575,7 +3575,7 @@
         <v>11</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>92.06</v>
+        <v>92.03</v>
       </c>
       <c r="I26" s="8" t="n">
         <v>4</v>
@@ -3631,7 +3631,7 @@
         <v>17</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>172.31</v>
+        <v>172.29</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>5</v>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>4 - 7W</t>
+          <t>4-7W Constant Current LED Driver, 300mA IP20 Rated Constant Current LED Driver Transformer, Converts AC85-265V into DC12-26V, IP20 Constant Current DC Transformers</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -5418,7 +5418,7 @@
         <v>56</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>729.6799999999999</v>
+        <v>729.67</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>987</v>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>IP67 15W Waterproof DC 12V LED Power Supply Driver Transformer AC 90-250V Flicker-free output, Outdoor transformer for garden lighting, pond water pumps</t>
+          <t>15W</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>LED Driver Power Supply 85V–265V DC Constant Current Transformer Adapter Flicker-Free Output For LED Strip Lights, LED Modules, and Power Accessories Indoor</t>
+          <t>12W</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>E27 ST64 Vintage LED Dimmable  Bulbs, 4W Edison Light Bulb, 2700K Warm White, Amber Retro Style Energy Saving Filament Decorative Bulbs</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>LED Driver Power Supply 85V–265V DC Constant Current Transformer Adapter Flicker-Free Output For LED Strip Lights, LED Modules, and Power Accessories Indoor</t>
+          <t>4-7W Constant Current LED Driver, 300mA IP20 Rated Constant Current LED Driver Transformer, Converts AC85-265V into DC12-26V, IP20 Constant Current DC Transformers</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -5602,7 +5602,7 @@
         <v>38</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>226.87</v>
+        <v>226.88</v>
       </c>
       <c r="J9" s="12" t="n">
         <v>260</v>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Combo Default Title.</t>
+          <t>LEDSone Industrial Pendant Light Retro Chandelier Ceiling Light Vintage Lamp Ceiling Lighting Metal Shade for Restaurant Living Room Bedroom Kitchen Hallway Bar (Nero interno bianco)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -5648,7 +5648,7 @@
         <v>31</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>629.03</v>
+        <v>629.04</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>491</v>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>E27 ST64 Vintage LED Dimmable  Bulbs, 8W Edison Light Bulb, 2700K Warm White, Amber Retro Style Energy Saving Filament Decorative Bulbs</t>
+          <t>1 PACK</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>IP67 30W Waterproof DC 12V LED Power Supply Driver Transformer AC 90-250V Flicker-free output, Outdoor transformer for garden lighting, pond water pumps</t>
+          <t>30W</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Black Colour Vintage Ceiling Rose Perfect for fabric flex cable, 100mm Metal Ceiling Light Fitting Plate with Accessories for Ceiling and Wall Lamp.</t>
+          <t>3.9 Inch Black Ceiling Canopy Kit Ceiling Plate, Modern Steel Canopy Kit Light Fixture for endant Light and Chandelier with All Hardware Includes Loop, Cross Bar and Mounting Screws.</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>DC 5V 50W 10Amp Power Supply Universal Regulated Switching AC to DC Converter AC110V/220V constant voltage Transformer Driver Adaptor for LED Strip Light, CCTV Camera Security System, Radio, Computer Project</t>
+          <t>50W</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>T connector</t>
+          <t>Boîte de jonction étanche IP68 - Connecteur de câble 3 voies - Connecteurs métalliques externes - Rallonge de boîte de jonction électrique - 3 voies pour câbles (1 paquet)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>LEDSone Metalen Easy Fit Lampenkap Retro Industriële Plafond Verlichting Schaduw Opknoping Hanger Schaduw Lichtpunt voor Keuken Eetkamer Lichten E27 (Blauw)</t>
+          <t>LEDSone Metall Lampenschirm Retro Industrielle Deckenbeleuchtung Pendelleuchte (Schwarz Innen Weiß, 2 Packung)</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Light Socket E27 Bulb Socket Ceramics Lamp Holder Lampshades addable ES Screw Bulb Lamp holder</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>DC VOLTAGE New Vintage Pendant Ceiling Shade Industrial Chandelier Flush Mount Lighting UK</t>
+          <t>Lampada a sospensione retrò E27 32 cm, lampada da soffitto in metallo, stile vintage, cavo regolabile - Faretto bianco per cucina, sala da pranzo, bar, caffetteria, ufficio (Verde)</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -6154,7 +6154,7 @@
         <v>22</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>467.78</v>
+        <v>467.79</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>200</v>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>IP67 150W Waterproof DC 12V LED Power Supply Driver Transformer AC 90-250V Flicker-free 2 output, Outdoor transformer for garden lighting, pond water pumps</t>
+          <t>12V 150W IP67 Waterproof LED Driver Transformer For Outdoor Lighting</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>LEDSone Industrial Pendant Light Retro Chandelier Ceiling Light Vintage Lamp Ceiling Lighting Metal Shade for Restaurant Living Room Bedroom Kitchen Hallway Bar (Grigio)</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Lámpara colgante industrial retro, lámpara de techo, lámpara vintage, iluminación de techo, pantalla de metal para (Negro, Sin bombilla)</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -6338,7 +6338,7 @@
         <v>22</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>427.43</v>
+        <v>427.44</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>372</v>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>IP67 36W Waterproof DC 12V LED Power Supply Driver Transformer AC 90-250V Flicker-free output, Outdoor transformer for garden lighting, pond water pumps</t>
+          <t>36W</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Yellow Brass Light Chain Pendant Light Fixture Chain, Vintage 32mm x 17mm Lighting Hanging Chain for lighting Ceiling lights, Pendant lights, Lamp fixtures, Chandeliers, for light weight.</t>
+          <t>LEDSone Heavy Chandelier Copper Light Chain 32mm x 17mm for Lighting Ceiling Lights Pendant Hanging Chain (Yellow Brass)</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Black / No</t>
+          <t>LEDSone Lámpara colgante de techo estilo retro industrial vintage con pantallas de cúpula curvada en color naranja, soporte E27 (Negro)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -6476,7 +6476,7 @@
         <v>20</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>394</v>
+        <v>394.01</v>
       </c>
       <c r="J28" s="8" t="n">
         <v>372</v>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-020_fast-moving-products/evidence/final_outputs/REQ-23_fast-moving-products/REQ-23-D01_fast_moving_products.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-020_fast-moving-products/evidence/final_outputs/REQ-23_fast-moving-products/REQ-23-D01_fast_moving_products.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>30-day = last 30 complete days; 90-day = last 90 complete days; both ending the last complete day. This run: 30d 2026-07-05 → 2026-08-03, 90d 2026-05-06 → 2026-08-03. Live data pulled 2026-08-04.</t>
+          <t>30-day = last 30 complete days; 90-day = last 90 complete days; both ending the last complete day. This run: 30d 2026-07-06 → 2026-08-04, 90d 2026-05-07 → 2026-08-04. Live data pulled 2026-08-05.</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Report window: 30-day 2026-07-05 → 2026-08-03  |  90-day 2026-05-06 → 2026-08-03  |  Currency € (EUR)  |  Live data pulled 2026-08-04  |  Ranked by 30-day units</t>
+          <t>Report window: 30-day 2026-07-06 → 2026-08-04  |  90-day 2026-05-07 → 2026-08-04  |  Currency € (EUR)  |  Live data pulled 2026-08-05  |  Ranked by 30-day units</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
         <v>25.5</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>289</v>
@@ -888,10 +888,10 @@
         <v>50</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -929,25 +929,25 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>134.4</v>
+        <v>153.08</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>3.22</v>
+        <v>2.54</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>3459</v>
+        <v>3438</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>3578</v>
+        <v>3125</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -966,44 +966,44 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>CRSF100BM</t>
+          <t>CCBKNWE12</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>5479679131815</t>
+          <t>5480982773927</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>3.9 Inch Black Ceiling Canopy Kit Ceiling Plate, Modern Steel Canopy Kit Light Fixture for endant Light and Chandelier with All Hardware Includes Loop, Cross Bar and Mounting Screws.</t>
+          <t>12W</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Ceiling Rose</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>149.5</v>
+        <v>226.88</v>
       </c>
       <c r="I7" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>8.67</v>
+        <v>10.67</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>3990</v>
+        <v>551</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>4604</v>
+        <v>517</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -1022,44 +1022,44 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ENC8459</t>
+          <t>CRSF100BM</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>15254086484233</t>
+          <t>5479679131815</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Grün / Ja</t>
+          <t>3.9 Inch Black Ceiling Canopy Kit Ceiling Plate, Modern Steel Canopy Kit Light Fixture for endant Light and Chandelier with All Hardware Includes Loop, Cross Bar and Mounting Screws.</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Uncategorised</t>
+          <t>Ceiling Rose</t>
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>506.5</v>
+        <v>149.5</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>25</v>
+        <v>8.67</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>8</v>
+        <v>3972</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>10</v>
+        <v>4583</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>Reorder soon</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -1078,44 +1078,44 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>COT9ABM</t>
+          <t>ENC8459</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>8361815638281</t>
+          <t>15254086484233</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Boîte de jonction étanche IP68 - Connecteur de câble 3 voies - Connecteurs métalliques externes - Rallonge de boîte de jonction électrique - 3 voies pour câbles (1 paquet)</t>
+          <t>Grün / Ja</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Connecter</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>99.84</v>
+        <v>506.5</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J9" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="K9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K9" s="12" t="n">
-        <v>58</v>
-      </c>
       <c r="L9" s="12" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>Promote / keep stock</t>
+          <t>Reorder soon</t>
         </is>
       </c>
     </row>
@@ -1134,44 +1134,44 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>LHTHE27BN</t>
+          <t>CCBKNWE7</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>8337016422665</t>
+          <t>7998061740297</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>4-7W Constant Current LED Driver, 300mA IP20 Rated Constant Current LED Driver Transformer, Converts AC85-265V into DC12-26V, IP20 Constant Current DC Transformers</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Lamp Holder</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>115.06</v>
+        <v>140.55</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>22</v>
+        <v>4.17</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>65</v>
+        <v>256</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>89</v>
+        <v>307</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>Promote / keep stock</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -1190,44 +1190,44 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>CCBKNWE12</t>
+          <t>COT9ABM</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>5480982773927</t>
+          <t>8361815638281</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>12W</t>
+          <t>Boîte de jonction étanche IP68 - Connecteur de câble 3 voies - Connecteurs métalliques externes - Rallonge de boîte de jonction électrique - 3 voies pour câbles (1 paquet)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Connecter</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>141.8</v>
+        <v>99.84</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>551</v>
+        <v>54</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>826</v>
+        <v>68</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Promote / keep stock</t>
         </is>
       </c>
     </row>
@@ -1246,53 +1246,53 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CNP1000YB</t>
+          <t>LDMST64E278</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>8381418864905</t>
+          <t>5478891749543</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>LEDSone Heavy Chandelier Copper Light Chain 32mm x 17mm for Lighting Ceiling Lights Pendant Hanging Chain (Yellow Brass)</t>
+          <t>1 PACK</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Small Categories</t>
+          <t>Bulbs</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>99.8</v>
+        <v>124.13</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>20</v>
+        <v>2.09</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>139</v>
+        <v>298</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>208</v>
+        <v>389</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>↓ Slowing</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -1302,53 +1302,53 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LHTHE27BN</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>5478891749543</t>
+          <t>8337016422665</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>1 PACK</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Bulbs</t>
+          <t>Lamp Holder</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>90.18000000000001</v>
+        <v>115.06</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>2.25</v>
+        <v>22</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>300</v>
+        <v>65</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>500</v>
+        <v>89</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>↓ Slowing</t>
+          <t>↑ Growing</t>
         </is>
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Promote / keep stock</t>
         </is>
       </c>
     </row>
@@ -1358,44 +1358,44 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+LHNSE27YB+LSHH240BM</t>
+          <t>CNP1000YB</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>7012415439015</t>
+          <t>8381418864905</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>24cm Black Inner White Metal Ceiling Lamp Shade - Easy Fit Light Pendant - Modern Ceiling Lighting Shade for Bedroom, Hallway, Office, Cafe, Restaurant -Industrial Light Shade</t>
+          <t>LEDSone Heavy Chandelier Copper Light Chain 32mm x 17mm for Lighting Ceiling Lights Pendant Hanging Chain (Yellow Brass)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Ceiling Lights with Shade</t>
+          <t>Small Categories</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>214.65</v>
+        <v>99.8</v>
       </c>
       <c r="I14" s="8" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>36</v>
+        <v>208</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>Promote / keep stock</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -1433,25 +1433,25 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>183.96</v>
+        <v>210.24</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>126</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
@@ -1470,44 +1470,44 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>12IP6730</t>
+          <t>CRSF100BM+LHNSE27YB+LSHH240BM</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>5480392163495</t>
+          <t>7012415439015</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>30W</t>
+          <t>24cm Black Inner White Metal Ceiling Lamp Shade - Easy Fit Light Pendant - Modern Ceiling Lighting Shade for Bedroom, Hallway, Office, Cafe, Restaurant -Industrial Light Shade</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Ceiling Lights with Shade</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>142.86</v>
+        <v>214.65</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>2.8</v>
+        <v>15</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Promote / keep stock</t>
         </is>
       </c>
     </row>
@@ -1526,53 +1526,53 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>LHSHE27BA</t>
+          <t>12IP6730</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>5481828778151</t>
+          <t>5480392163495</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>30W</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Lamp Holder</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>77.87</v>
+        <v>152.85</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>1030</v>
+        <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>2377</v>
+        <v>140</v>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>↑ Growing</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -1582,53 +1582,53 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CRSF100YB+WSSS70YB+LSFT220BC</t>
+          <t>PHUH0.5HETBM</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>15624329134345</t>
+          <t>8436434862345</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Gebürstetes Kupfer / Ohne Leuchtmittel</t>
+          <t>0.5m Hemp Pendant holder</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Uncategorised</t>
+          <t>Hemp Lighting</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>188.04</v>
+        <v>113.35</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>12</v>
+        <v>1.88</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>182</v>
+        <v>36</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>↓ Slowing</t>
         </is>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Maintain stock</t>
         </is>
       </c>
     </row>
@@ -1638,53 +1638,53 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>WSNWBM+LSCY290BM+LDMST64E274</t>
+          <t>LHSHE27BA</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>15601922507017</t>
+          <t>5481828778151</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Applique Parete Vintage Industriale Metallo Lampada da Muro Impermeabile Esterno Interno Attacco E27 Luce Retrò per Ingresso, Giardino, Bar, Ristorante (Curvy - Nero)</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Uncategorised</t>
+          <t>Lamp Holder</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>211</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>3.67</v>
+        <v>2.5</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>77</v>
+        <v>1026</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>210</v>
+        <v>2052</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>WSNWBM+LSCY290BM</t>
+          <t>WSNWBM+LSCY290BM+LDMST64E274</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Kurvig / Nein</t>
+          <t>Applique Parete Vintage Industriale Metallo Lampada da Muro Impermeabile Esterno Interno Attacco E27 Luce Retrò per Ingresso, Giardino, Bar, Ristorante (Curvy - Nero)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -1713,25 +1713,25 @@
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>184.58</v>
+        <v>250.48</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>4</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
@@ -1750,44 +1750,44 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>LDST185E274</t>
+          <t>CRSF100YB+WSSS70YB+LSFT220BC</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>15293107896585</t>
+          <t>15624329134345</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>1 Pack</t>
+          <t>Gebürstetes Kupfer / Ohne Leuchtmittel</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Bulbs</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>66.88</v>
+        <v>188.04</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>3.67</v>
+        <v>12</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>1079</v>
+        <v>73</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>2943</v>
+        <v>182</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -1806,17 +1806,17 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CRSF100YB+LHNSE27YB+SCRN70YB+LSCY290BS</t>
+          <t>WSNWBM+LSCY290BM</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>15610680738057</t>
+          <t>15601922507017</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Brushed Silver</t>
+          <t>Kurvig / Nein</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -1825,25 +1825,25 @@
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>196.9</v>
+        <v>184.58</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>10</v>
+        <v>2.75</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>181</v>
+        <v>75</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>543</v>
+        <v>205</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -1862,109 +1862,105 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHHT1PBRBM+LSMS320BI</t>
+          <t>12BO72</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>8178462523657</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>6901461385383</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr"/>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Half thin Holder Pendant Light</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>170.1</v>
+        <v>120.89</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>432</v>
+        <v>60</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>Maintain stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>LDST185E274</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>15293107896585</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>1 Pack</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Bulbs</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>66.88</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="K24" s="8" t="n">
+        <v>1079</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>2943</v>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
           <t>↑ Growing</t>
         </is>
       </c>
-      <c r="N23" s="10" t="inlineStr">
+      <c r="N24" s="6" t="inlineStr">
         <is>
           <t>Overstocked – review</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>PHUH1HETBM</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>7542206660838</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>1m Hemp Pendant holder</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>Hemp Lighting</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G24" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="H24" s="17" t="n">
-        <v>167</v>
-      </c>
-      <c r="I24" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="14" t="inlineStr">
-        <is>
-          <t>↑ Growing</t>
-        </is>
-      </c>
-      <c r="N24" s="14" t="inlineStr">
-        <is>
-          <t>Restock immediately</t>
         </is>
       </c>
     </row>
@@ -1974,53 +1970,49 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>COT9ABM6PK</t>
+          <t>LHSHE27YB</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>15183418786057</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>6 Pack</t>
-        </is>
-      </c>
+          <t>7748182868198</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr"/>
       <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Uncategorised</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>89.59999999999999</v>
+        <v>65.89</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>3.33</v>
+        <v>1.83</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>9</v>
+        <v>819</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>27</v>
+        <v>2234</v>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>↓ Slowing</t>
         </is>
       </c>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>Reorder soon</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -2030,53 +2022,53 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>PHUH0.5HETBM</t>
+          <t>CRSF100YB+LHNSE27YB+SCRN70YB+LSCY290BS</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>8436434862345</t>
+          <t>15610680738057</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>0.5m Hemp Pendant holder</t>
+          <t>Brushed Silver</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Hemp Lighting</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
         <v>10</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>78.90000000000001</v>
+        <v>196.9</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1.67</v>
+        <v>10</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>54</v>
+        <v>543</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>↓ Slowing</t>
+          <t>↑ Growing</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>Maintain stock</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -2086,22 +2078,22 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>CCBKNWE12</t>
+          <t>CRSF100BM+PHHT1PBRBM+LSMS320BI</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>8279101899017</t>
+          <t>8178462523657</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>12W</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Half thin Holder Pendant Light</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
@@ -2111,84 +2103,84 @@
         <v>10</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>70.90000000000001</v>
+        <v>170.1</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>144</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>432</v>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>↑ Growing</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>Overstocked – review</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>PHUH1HETBM</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>7542206660838</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>1m Hemp Pendant holder</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>Hemp Lighting</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="K27" s="12" t="n">
-        <v>551</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>1653</v>
-      </c>
-      <c r="M27" s="10" t="inlineStr">
+      <c r="G28" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>167</v>
+      </c>
+      <c r="I28" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="14" t="inlineStr">
         <is>
           <t>↑ Growing</t>
         </is>
       </c>
-      <c r="N27" s="10" t="inlineStr">
-        <is>
-          <t>Overstocked – review</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>CCBKNWE7</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>7998061740297</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>4-7W Constant Current LED Driver, 300mA IP20 Rated Constant Current LED Driver Transformer, Converts AC85-265V into DC12-26V, IP20 Constant Current DC Transformers</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>Transformer</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G28" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="H28" s="9" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="I28" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="K28" s="8" t="n">
-        <v>260</v>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>780</v>
-      </c>
-      <c r="M28" s="6" t="inlineStr">
-        <is>
-          <t>↑ Growing</t>
-        </is>
-      </c>
-      <c r="N28" s="6" t="inlineStr">
-        <is>
-          <t>Overstocked – review</t>
+      <c r="N28" s="14" t="inlineStr">
+        <is>
+          <t>Restock immediately</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2228,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Report window: 30-day 2026-07-05 → 2026-08-03  |  90-day 2026-05-06 → 2026-08-03  |  Currency € (EUR)  |  Live data pulled 2026-08-04  |  Ranked by 30-day units</t>
+          <t>Report window: 30-day 2026-07-06 → 2026-08-04  |  90-day 2026-05-07 → 2026-08-04  |  Currency € (EUR)  |  Live data pulled 2026-08-05  |  Ranked by 30-day units</t>
         </is>
       </c>
     </row>
@@ -2337,25 +2329,25 @@
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>629.04</v>
+        <v>670.7</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>475</v>
+        <v>430</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -2452,10 +2444,10 @@
         <v>22</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>467.79</v>
+        <v>467.44</v>
       </c>
       <c r="I6" s="8" t="n">
         <v>15</v>
@@ -2464,10 +2456,10 @@
         <v>1.47</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -2542,17 +2534,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290BM</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290GY</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>B0DLWRP73C</t>
+          <t>B0CN34J7VX</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Lámpara colgante industrial retro, lámpara de techo, lámpara vintage, iluminación de techo, pantalla de metal para (Negro, Sin bombilla)</t>
+          <t>LEDSone Industrial Pendant Light Retro Chandelier Ceiling Light Vintage Lamp Ceiling Lighting Metal Shade for Restaurant Living Room Bedroom Kitchen Hallway Bar (Grigio)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -2561,29 +2553,29 @@
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>378.39</v>
+        <v>434.13</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>587</v>
+        <v>503</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>↑ Growing</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
@@ -2598,32 +2590,32 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>WCB7BM+RPR44WH</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290BM</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>B09MQRGZMT</t>
+          <t>B0DLWRP73C</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Abat-jour noir en forme de tambour en métal avec cage métallique, style industriel facile à installer pour plafond d'intérieur et cuisine, salon, couloir (noir)</t>
+          <t>Lámpara colgante industrial retro, lámpara de techo, lámpara vintage, iluminación de techo, pantalla de metal para (Negro, Sin bombilla)</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Wire Cage</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
         <v>18</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>183.19</v>
+        <v>358.82</v>
       </c>
       <c r="I9" s="12" t="n">
         <v>11</v>
@@ -2632,19 +2624,19 @@
         <v>1.64</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>112</v>
+        <v>369</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>187</v>
+        <v>615</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -2654,44 +2646,44 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>CRSF100CH+PHCHPCRCH+LSMS320OR</t>
+          <t>WCB7BM+RPR44WH</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>B09GKT6DJC</t>
+          <t>B09MQRGZMT</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Lampada a sospensione retrò E27 32 cm, lampada da soffitto in metallo, stile vintage, cavo regolabile - Faretto bianco per cucina, sala da pranzo, bar, caffetteria, ufficio (Arancia)</t>
+          <t>Abat-jour noir en forme de tambour en métal avec cage métallique, style industriel facile à installer pour plafond d'intérieur et cuisine, salon, couloir (noir)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Uncategorised</t>
+          <t>Wire Cage</t>
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>256.01</v>
+        <v>183.19</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>500</v>
+        <v>187</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -2700,7 +2692,7 @@
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -2710,44 +2702,44 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290GY</t>
+          <t>CCBC7</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>B0CN34J7VX</t>
+          <t>B097TVZ186</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>LEDSone Industrial Pendant Light Retro Chandelier Ceiling Light Vintage Lamp Ceiling Lighting Metal Shade for Restaurant Living Room Bedroom Kitchen Hallway Bar (Grigio)</t>
+          <t>7W Konstantstrom-LED-Netzteil Elektronischer Treiber</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Uncategorised</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>229.8</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>1.33</v>
+        <v>5</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>372</v>
+        <v>263</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>930</v>
+        <v>526</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
@@ -2766,44 +2758,44 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>LSCY210BG3PK+RPR44WH3PK</t>
+          <t>CRSF100BM+PHCH1BMRBM+LSCY290BM</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>B0CS9PS8J3</t>
+          <t>B0DCVYB6D5</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>DCVoltage 3 Pack Vintage Metal Lampshade 21cm Easy to Assemble Black Gold Lamp Shade for Living Room Bedroom Kitchen Cafe Restaurant (Style 5)</t>
+          <t>LEDSone Lámpara colgante de techo estilo retro industrial vintage con pantallas de cúpula curvada en color naranja, soporte E27 (Negro)</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Lampshade</t>
+          <t>Special-pr</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>349.7</v>
+        <v>246.89</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>1017</v>
+        <v>922</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -2822,32 +2814,32 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>CRSF100CH+PHCHPCRCH+LSMS320RE</t>
+          <t>LSCY210BG3PK+RPR44WH3PK</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>B09GKQWSF5</t>
+          <t>B0CS9PS8J3</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Lampada a sospensione retrò E27 32 cm, lampada da soffitto in metallo, stile vintage, cavo regolabile - Faretto bianco per cucina, sala da pranzo, bar, caffetteria, ufficio (Rosso)</t>
+          <t>DCVoltage 3 Pack Vintage Metal Lampshade 21cm Easy to Assemble Black Gold Lamp Shade for Living Room Bedroom Kitchen Cafe Restaurant (Style 5)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Uncategorised</t>
+          <t>Lampshade</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
         <v>11</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>231.11</v>
+        <v>349.7</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>11</v>
@@ -2856,10 +2848,10 @@
         <v>1</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>200</v>
+        <v>372</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>545</v>
+        <v>1015</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -2878,44 +2870,44 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>LSMS320GR+RPR44WH</t>
+          <t>CRSF100CH+PHCHPCRCH+LSMS320OR</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>B093H9DJK7</t>
+          <t>B09GKT6DJC</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Industrial Green Lampshade Metal  32cm Easy Fit With Reducer Plate Modern Hanging Pendant Light Shade for Bedroom, Hallway, Office, Kitchen, Dining Room, Cafe, Bar, Restaurtant</t>
+          <t>Lampada a sospensione retrò E27 32 cm, lampada da soffitto in metallo, stile vintage, cavo regolabile - Faretto bianco per cucina, sala da pranzo, bar, caffetteria, ufficio (Arancia)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Lampshade</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
         <v>11</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>122.67</v>
+        <v>234.76</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>770</v>
+        <v>192</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>2100</v>
+        <v>524</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -2934,17 +2926,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290GY</t>
+          <t>CRSF100CH+PHCHPCRCH+LSMS320RE</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>B0DLWRFKRQ</t>
+          <t>B09GKQWSF5</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>LEDSone Industrial Pendant Light Retro Chandelier Ceiling Light Vintage Lamp Ceiling Lighting Metal Shade for Restaurant Living Room Bedroom Kitchen Hallway Bar (Grigio)</t>
+          <t>Lampada a sospensione retrò E27 32 cm, lampada da soffitto in metallo, stile vintage, cavo regolabile - Faretto bianco per cucina, sala da pranzo, bar, caffetteria, ufficio (Rosso)</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -2953,25 +2945,25 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>204.33</v>
+        <v>231.11</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>372</v>
+        <v>192</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>1116</v>
+        <v>524</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
@@ -2990,44 +2982,44 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CCBC7</t>
+          <t>LSMS320GR+RPR44WH</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>B097TVZ186</t>
+          <t>B093H9DJK7</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>7W Konstantstrom-LED-Netzteil Elektronischer Treiber</t>
+          <t>Industrial Green Lampshade Metal  32cm Easy Fit With Reducer Plate Modern Hanging Pendant Light Shade for Bedroom, Hallway, Office, Kitchen, Dining Room, Cafe, Bar, Restaurtant</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Lampshade</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>49.5</v>
+        <v>122.67</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>10</v>
+        <v>1.57</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>263</v>
+        <v>768</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>789</v>
+        <v>2095</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -3046,44 +3038,40 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHCH1BMRBM+LSCY290BM</t>
+          <t>CRSF100GB+PHCHPBRGB+LSCY290GB</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>B0DCVYB6D5</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>LEDSone Lámpara colgante de techo estilo retro industrial vintage con pantallas de cúpula curvada en color naranja, soporte E27 (Negro)</t>
-        </is>
-      </c>
+          <t>B096G8PC4S</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr"/>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Special-pr</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>181.34</v>
+        <v>273.25</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>1.8</v>
+        <v>3.33</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>372</v>
+        <v>73</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>1240</v>
+        <v>219</v>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
@@ -3092,7 +3080,7 @@
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -3102,44 +3090,40 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290GR</t>
+          <t>LSMS320OR+RPR44WH</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>B0CN34CLZG</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Industriel Suspension Luminaire Rétro Lustre Plafonnier Vintage Lampe Éclairage de Plafond Abat-jour en Métal pour Restaurant Salon Chambre Cuisine Couloir Bar (Vert)</t>
-        </is>
-      </c>
+          <t>B08TX2CXR6</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Uncategorised</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>175.3</v>
+        <v>139.63</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>372</v>
+        <v>262</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>1240</v>
+        <v>786</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -3158,44 +3142,40 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>CRSF100BM+WSHR135BM+LSFT220GY</t>
+          <t>LSCP150YE+RPR44WH</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>B0C5HM7899</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Applique Murale Vintage Antique en Métal, Applique de Plafond Rétro E27 pour Chambre à Coucher, Salle à Manger, Restaurant, Bar, Galeries (Grey)</t>
-        </is>
-      </c>
+          <t>B0BWTX5K2W</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr"/>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Wall sconce</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>148.92</v>
+        <v>111.62</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>9</v>
+        <v>1.43</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>203</v>
+        <v>60</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
@@ -3204,7 +3184,7 @@
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Promote / keep stock</t>
         </is>
       </c>
     </row>
@@ -3214,48 +3194,44 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>LSMS320BG+RPR44WH</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290YE</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>B0F2F8SKBV</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>LEDSONE Endüstriyel Abajur Metal Siyah İç Altın 32 cm Redüktör Plakalı Kolay Uyum Modern Asma Asma Işık Gölgesi Yatak Odası, Koridor, Ofis, Mutfak, Yemek Odası, Kafe, Bar, Restoran için</t>
-        </is>
-      </c>
+          <t>B0DM1Z7LKF</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr"/>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Lampshade</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
         <v>9</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>132.88</v>
+        <v>189.3</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>1107</v>
+        <v>1230</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>↑ Growing</t>
         </is>
       </c>
       <c r="N20" s="6" t="inlineStr">
@@ -3270,109 +3246,105 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>CCBKNWE7</t>
+          <t>LSCY290BC+RPR44WH</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>B098QLF674</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>4-7W Constant Current LED Driver, 300mA IP20 Rated Constant Current LED Driver Transformer, Converts AC85-265V into DC12-26V, IP20 Constant Current DC Transformers</t>
-        </is>
-      </c>
+          <t>B093HCQGSL</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr"/>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
         <v>9</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>49.49</v>
+        <v>152.94</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>260</v>
+        <v>148</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>867</v>
+        <v>493</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>Overstocked – review</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>CRSF100BM+WSHR135BM+LSFT220GY</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>B0C5HM7899</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Applique Murale Vintage Antique en Métal, Applique de Plafond Rétro E27 pour Chambre à Coucher, Salle à Manger, Restaurant, Bar, Galeries (Grey)</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Wall sconce</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>148.92</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>203</v>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
           <t>↑ Growing</t>
         </is>
       </c>
-      <c r="N21" s="10" t="inlineStr">
-        <is>
-          <t>Overstocked – review</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>PHSF1PWR40WH+LSBS160GR</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>B0DGQK62BD</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>LEDSone Modern Teardrop Orange Pendant Shade Industrial Hanging Ceiling Lighting Ideal for Dining Rooms, Bars, Clubs and Restaurants (Verde)</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>Pendant light with shade</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="G22" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="H22" s="17" t="n">
-        <v>179.12</v>
-      </c>
-      <c r="I22" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="K22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="14" t="inlineStr">
-        <is>
-          <t>↑ Growing</t>
-        </is>
-      </c>
-      <c r="N22" s="14" t="inlineStr">
-        <is>
-          <t>Restock immediately</t>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -3382,48 +3354,44 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>CRSF100BM+LHNSE27BM+SCRN70YB+LSMS320RE</t>
+          <t>LSCY290WH+RPR44WH</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>B09LMKNDW7</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Industrial Semi-Flush Mount Ceiling Lights Metal Curve Shade E27 Base Lamp Holder Vintage Style Ceiling Lighting Lamp for Living Hallway Ceiling Metal Large Rustic 32cm Shade Pendant (Red)</t>
-        </is>
-      </c>
+          <t>B093T4L68X</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr"/>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Curvy ceiling light</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>155.93</v>
+        <v>132.48</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J23" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>475</v>
+        <v>688</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>1781</v>
+        <v>2293</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>↓ Slowing</t>
         </is>
       </c>
       <c r="N23" s="10" t="inlineStr">
@@ -3438,44 +3406,44 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>PHHCF1BMRBM</t>
+          <t>CCBKNWE7</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>B0GF2BBSZL</t>
+          <t>B098QLF674</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>LEDSone Heavy Duty Vintage Pendant Light Kit with 1m Hanging Chain E27 Lamp Holder Black 3 Core Cable Adjustable for Custom Length DIY Ceiling Lighting Kit for Home, Kitchen, Bar</t>
+          <t>4-7W Constant Current LED Driver, 300mA IP20 Rated Constant Current LED Driver Transformer, Converts AC85-265V into DC12-26V, IP20 Constant Current DC Transformers</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Herder Holder Pedant</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>155.24</v>
+        <v>49.49</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>18</v>
+        <v>256</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>68</v>
+        <v>853</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
@@ -3484,7 +3452,7 @@
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>Promote / keep stock</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -3494,22 +3462,22 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>IMRECPK</t>
+          <t>PHSF1PWR40WH+LSBS160GR</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0C5TGQTJC</t>
+          <t>B0DGQK62BD</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>12V LED Module Light 20 Pcs Red IP65 Waterproof Injection Light for Sign Board, Shop Name, Letter Sign, Backlight Decoration, Energy Saving DIY Lighting (red 20 pack)</t>
+          <t>LEDSone Modern Teardrop Orange Pendant Shade Industrial Hanging Ceiling Lighting Ideal for Dining Rooms, Bars, Clubs and Restaurants (Verde)</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>LED Module</t>
+          <t>Pendant light with shade</t>
         </is>
       </c>
       <c r="F25" s="16" t="n">
@@ -3519,7 +3487,7 @@
         <v>8</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>116.91</v>
+        <v>179.12</v>
       </c>
       <c r="I25" s="16" t="n">
         <v>1</v>
@@ -3550,48 +3518,44 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>WSFS1BMBM</t>
+          <t>CRSF100CH+PHCHPCRCH+LSMS320WH</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>B09VZBPGYR</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>LEDSOne Aplique de pared industrial, lámpara de pared vintage negra de 180 grados, casquillo E27, tipo de tornillo, lámpara de pared antigua ajustable para restaurantes, cocina, dormitorio.</t>
-        </is>
-      </c>
+          <t>B0DYTZ2K5D</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr"/>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Wall sconce</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F26" s="8" t="n">
         <v>8</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>92.03</v>
+        <v>169</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>394</v>
+        <v>720</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
@@ -3606,44 +3570,44 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>CRSF100BM2PK+PHHT1PBRBM2PK</t>
+          <t>CRSF100BM+LHNSE27BM+SCRN70YB+LSMS320RE</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>B0DJFJ2Z4Y</t>
+          <t>B09LMKNDW7</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>2 Pack Black Ceiling Pendant Light E27 95cm Adjustable Cable</t>
+          <t>Industrial Semi-Flush Mount Ceiling Lights Metal Curve Shade E27 Base Lamp Holder Vintage Style Ceiling Lighting Lamp for Living Hallway Ceiling Metal Large Rustic 32cm Shade Pendant (Red)</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Half thin Holder Pendant Light</t>
+          <t>Curvy ceiling light</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>172.29</v>
+        <v>155.93</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>72</v>
+        <v>469</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>309</v>
+        <v>1759</v>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
@@ -3652,7 +3616,7 @@
       </c>
       <c r="N27" s="10" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -3662,44 +3626,44 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHCH1BMRBM+LSCY290GR</t>
+          <t>PHHCF1BMRBM</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>B0DCVZSW3T</t>
+          <t>B0GF2BBSZL</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>LEDSone Lámpara de araña moderna vintage con pantalla colgante industrial para techo, ideal para comedor, bar, club, base E27 (verde)</t>
+          <t>LEDSone Heavy Duty Vintage Pendant Light Kit with 1m Hanging Chain E27 Lamp Holder Black 3 Core Cable Adjustable for Custom Length DIY Ceiling Lighting Kit for Home, Kitchen, Bar</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Curvy Holder Pendant</t>
+          <t>Herder Holder Pedant</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>148.32</v>
+        <v>155.24</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>372</v>
+        <v>17</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>1594</v>
+        <v>64</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -3708,7 +3672,7 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Promote / keep stock</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3720,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Report window: 30-day 2026-07-05 → 2026-08-03  |  90-day 2026-05-06 → 2026-08-03  |  Currency € (EUR)  |  Live data pulled 2026-08-04  |  Ranked by 30-day units</t>
+          <t>Report window: 30-day 2026-07-06 → 2026-08-04  |  90-day 2026-05-07 → 2026-08-04  |  Currency € (EUR)  |  Live data pulled 2026-08-05  |  Ranked by 30-day units</t>
         </is>
       </c>
     </row>
@@ -3838,48 +3802,48 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRYB+SCRN70BM+LSOL180BG</t>
+          <t>12IP6715</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>405554723464</t>
+          <t>394458014499</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Combo Default Title.</t>
+          <t>15W</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Uncategorised</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>455.4</v>
+        <v>245.24</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>23</v>
+        <v>1.23</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>99</v>
+        <v>381</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>129</v>
+        <v>357</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
@@ -3894,17 +3858,17 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>5IP2050</t>
+          <t>12IP6736</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>394444713965</t>
+          <t>163956259736</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>50W</t>
+          <t>36W</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -3913,34 +3877,34 @@
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>169.66</v>
+        <v>354.08</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>1.13</v>
+        <v>1.86</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>131</v>
+        <v>355</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>231</v>
+        <v>410</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -3950,53 +3914,53 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>COS93BM2PK</t>
+          <t>CRSF100BM+PHSH1PBRYB+SCRN70BM+LSOL180BG</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>394976085481</t>
+          <t>405554723464</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Combo Default Title.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Connecter</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>124.08</v>
+        <v>455.4</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1.2</v>
+        <v>23</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>962</v>
+        <v>99</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>2405</v>
+        <v>129</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>↑ Growing</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -4006,53 +3970,53 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>WJBIP68T13BM2PK</t>
+          <t>24IP2048</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>167609977844</t>
+          <t>394444713965</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Combo Default Title.</t>
+          <t>2A 48W</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Junction Box</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>131.55</v>
+        <v>169.36</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>2.2</v>
+        <v>1.27</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>466</v>
+        <v>114</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -4062,44 +4026,44 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>24IP2048</t>
+          <t>COS93BM2PK</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>394444713965</t>
+          <t>394976085481</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>2A 48W</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Connecter</t>
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>108.79</v>
+        <v>194.66</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>72</v>
+        <v>956</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>196</v>
+        <v>1593</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -4108,7 +4072,7 @@
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -4118,53 +4082,53 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>LHSHE27GB</t>
+          <t>12IP20150</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>165238748752</t>
+          <t>163935836148</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>DC Voltage Bottle Lamp Holder Light Bulb Socket E27 Base</t>
+          <t>12V 13A 150W, DC Universal Regulated Switching Power Supply, 110V AC to DC 12 Volt LED Driver, Converter, Transformer for LED Strip Light.</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Lamp Holder</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>63.32</v>
+        <v>330.45</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>5.5</v>
+        <v>2.29</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>801</v>
+        <v>89</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>2185</v>
+        <v>167</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -4174,17 +4138,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>12IP20150</t>
+          <t>12IP2080</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>163935836148</t>
+          <t>397695063556</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>12V 13A 150W, DC Universal Regulated Switching Power Supply, 110V AC to DC 12 Volt LED Driver, Converter, Transformer for LED Strip Light.</t>
+          <t>80w</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -4193,34 +4157,34 @@
         </is>
       </c>
       <c r="F10" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>243.72</v>
+      </c>
+      <c r="I10" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="G10" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>193.5</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="J10" s="7" t="n">
-        <v>10</v>
+        <v>1.6</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>89</v>
+        <v>297</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>267</v>
+        <v>557</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -4230,44 +4194,40 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>CRSF100CO+CL3TBR+LHSHE27YB</t>
+          <t>12IP2040</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>165420199216</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Copper / Brown / Yellow Brass</t>
-        </is>
-      </c>
+          <t>394444713965</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr"/>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Pendant lights without shade</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>110</v>
+        <v>177.5</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>10</v>
+        <v>1.14</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>557</v>
+        <v>117</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>1671</v>
+        <v>219</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
@@ -4276,7 +4236,7 @@
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -4286,44 +4246,44 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>CL3TBR</t>
+          <t>5IP2050</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>164828759593</t>
+          <t>394444713965</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1 M</t>
+          <t>50W</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>19.5</v>
+        <v>159.78</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>10</v>
+        <v>1.07</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>557</v>
+        <v>131</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>1671</v>
+        <v>246</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -4332,7 +4292,7 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -4342,17 +4302,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>CCGNNWE24</t>
+          <t>12IP6730</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>394789658453</t>
+          <t>394458014499</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>LED Trafo 24W Treiber Driver 600mA Elektronisch Netzteil Transformator</t>
+          <t>30W</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -4361,25 +4321,25 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>82.44</v>
+        <v>206.21</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>540</v>
+        <v>140</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -4388,7 +4348,7 @@
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -4398,53 +4358,53 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>12IP6715</t>
+          <t>WJBIP68T13BM2PK</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>394458014499</t>
+          <t>167609977844</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>15W</t>
+          <t>Combo Default Title.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Junction Box</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>80.55</v>
+        <v>174.37</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1</v>
+        <v>1.88</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>381</v>
+        <v>171</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>1270</v>
+        <v>342</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>↑ Growing</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -4454,48 +4414,44 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>LHTHE27GB</t>
+          <t>12IP6710</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>167596164116</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Green Brass</t>
-        </is>
-      </c>
+          <t>394458014499</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr"/>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Lamp Holder</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>69.95</v>
+        <v>113.45</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>1.8</v>
+        <v>1.15</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>114</v>
+        <v>380</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>380</v>
+        <v>760</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>↓ Slowing</t>
         </is>
       </c>
       <c r="N15" s="10" t="inlineStr">
@@ -4510,53 +4466,49 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHRI1PBRBY+LSDO210BB+ICST64E27</t>
+          <t>HLHG120CH2PK</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>406891898916</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Nein / Gebürstetes Messing</t>
-        </is>
-      </c>
+          <t>406114835830</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
       <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Uncategorised</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>199.12</v>
+        <v>112.54</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>8</v>
+        <v>1.67</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>9</v>
+        <v>213</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>34</v>
+        <v>426</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>Promote / keep stock</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -4566,53 +4518,49 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>WLGI350E27BM</t>
+          <t>12IP20100</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>407077056567</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>350 mm H x 230 mm B ohne Arm</t>
-        </is>
-      </c>
+          <t>394444713965</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr"/>
       <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Uncategorised</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>135.92</v>
+        <v>233.84</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>2.67</v>
+        <v>1.08</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>64</v>
+        <v>191</v>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>Promote / keep stock</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -4622,53 +4570,49 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>12IP6730</t>
+          <t>COS93BM</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>394458014499</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>30W</t>
-        </is>
-      </c>
+          <t>167669451899</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>113.52</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>70</v>
+        <v>1912</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>262</v>
+        <v>4412</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>↓ Slowing</t>
         </is>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -4678,48 +4622,48 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>LSOL180BG+RPR44WH</t>
+          <t>LHSHE27GB</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>336646664856</t>
+          <t>165238748752</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Lampenschirm Metall Schwarz Gold 18cm E27 Pendelleuchte Industrie Vintage Küche</t>
+          <t>DC Voltage Bottle Lamp Holder Light Bulb Socket E27 Base</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Lampshade</t>
+          <t>Lamp Holder</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>103.92</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>8</v>
+        <v>3.25</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>273</v>
+        <v>801</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>1024</v>
+        <v>1848</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N19" s="10" t="inlineStr">
@@ -4734,44 +4678,40 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE7</t>
+          <t>24IP67120</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>394417592862</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>4-7W Constant Current LED Driver, 300mA IP20 Rated Constant Current LED Driver Transformer, Converts AC85-265V into DC12-26V, IP20 Constant Current DC Transformers</t>
-        </is>
-      </c>
+          <t>394458014499</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr"/>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>298.64</v>
+      </c>
+      <c r="I20" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G20" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>55.92</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>4</v>
-      </c>
       <c r="J20" s="7" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>260</v>
+        <v>17</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>975</v>
+        <v>46</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
@@ -4780,7 +4720,7 @@
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Promote / keep stock</t>
         </is>
       </c>
     </row>
@@ -4790,44 +4730,40 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>CL3RHE</t>
+          <t>12IP20360</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>165082859660</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>1 M</t>
-        </is>
-      </c>
+          <t>163935836148</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr"/>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>15.6</v>
+        <v>283.57</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>515</v>
+        <v>81</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>1931</v>
+        <v>221</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
@@ -4836,7 +4772,7 @@
       </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -4846,44 +4782,40 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHHT1PBRBM+LSMS320BI</t>
+          <t>12SIP67100</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>394896227598</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>317084364841</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr"/>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Half thin Holder Pendant Light</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>152.95</v>
+        <v>230.23</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>617</v>
+        <v>49</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -4892,7 +4824,7 @@
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Promote / keep stock</t>
         </is>
       </c>
     </row>
@@ -4902,48 +4834,44 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>12IP2080</t>
+          <t>12IP20120</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>397695063556</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>80w</t>
-        </is>
-      </c>
+          <t>394418832707</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr"/>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>108.43</v>
+        <v>202.84</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>3.5</v>
+        <v>1.22</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>297</v>
+        <v>135</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>1273</v>
+        <v>368</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N23" s="10" t="inlineStr">
@@ -4958,48 +4886,44 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>12IP6736</t>
+          <t>24IP6710</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>394458014499</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>36W</t>
-        </is>
-      </c>
+          <t>167186637395</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>77.27</v>
+      </c>
+      <c r="I24" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>107.73</v>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>5</v>
-      </c>
       <c r="J24" s="7" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>355</v>
+        <v>196</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>1521</v>
+        <v>535</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N24" s="6" t="inlineStr">
@@ -5014,53 +4938,49 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>CCBKNWE25</t>
+          <t>WJBIP685BM2PK</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>394417592862</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>18-25W 300mA DC54-87V Compact Constant Current LED Driver Electronic Transformer</t>
-        </is>
-      </c>
+          <t>167609977844</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr"/>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>76.93000000000001</v>
+        <v>131.11</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>320</v>
+        <v>29</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>1371</v>
+        <v>87</v>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Maintain stock</t>
         </is>
       </c>
     </row>
@@ -5070,17 +4990,17 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>12IP2030</t>
+          <t>12BO48</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>394444713965</t>
+          <t>163935831038</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>30w</t>
+          <t>LED 48W Power Adapter Driver DC12V LED Transformer for LED Strips/MR16/CCTV</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -5089,25 +5009,25 @@
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>69.93000000000001</v>
+        <v>117.85</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>163</v>
+        <v>366</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -5116,7 +5036,7 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -5126,44 +5046,44 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>12DE2P2A</t>
+          <t>CRSF100CO+CL3TBR+LHSHE27YB</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>316699359122</t>
+          <t>165420199216</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>Copper / Brown / Yellow Brass</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Pendant lights without shade</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>64.08</v>
+        <v>110</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>1.75</v>
+        <v>10</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>793</v>
+        <v>557</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>3399</v>
+        <v>1671</v>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
@@ -5182,17 +5102,17 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE12</t>
+          <t>12IP2030</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>405328533644</t>
+          <t>394444713965</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>12W</t>
+          <t>30w</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -5201,34 +5121,34 @@
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>58.03</v>
+        <v>96.38</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>3.5</v>
+        <v>1.11</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>551</v>
+        <v>38</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>2361</v>
+        <v>114</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>↑ Growing</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Monitor</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5194,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Per shared internal SKU, last 30 days 2026-07-05 → 2026-08-03  |  Currency €  |  Stock Cover Days = Current Stock ÷ (30-day units ÷ 30)  |  Live data 2026-08-04</t>
+          <t>Per shared internal SKU, last 30 days 2026-07-06 → 2026-08-04  |  Currency €  |  Stock Cover Days = Current Stock ÷ (30-day units ÷ 30)  |  Live data 2026-08-05</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5295,7 @@
         <v>742.24</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K4" s="8" t="n">
         <v>254</v>
@@ -5421,10 +5341,10 @@
         <v>729.67</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
@@ -5438,12 +5358,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>12IP6715</t>
+          <t>CCBKNWE7</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>15W</t>
+          <t>4-7W Constant Current LED Driver, 300mA IP20 Rated Constant Current LED Driver Transformer, Converts AC85-265V into DC12-26V, IP20 Constant Current DC Transformers</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -5452,25 +5372,25 @@
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>43</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>328.98</v>
+        <v>252.33</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>381</v>
+        <v>256</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>266</v>
+        <v>179</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -5484,12 +5404,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>CCBKNWE12</t>
+          <t>12IP6715</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>12W</t>
+          <t>15W</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -5501,26 +5421,26 @@
         <v>0</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>284.91</v>
+        <v>319.54</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>551</v>
+        <v>381</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>424</v>
+        <v>272</v>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Sufficient stock</t>
         </is>
       </c>
     </row>
@@ -5550,19 +5470,19 @@
         <v>7</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>194.45</v>
+        <v>199.14</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>3459</v>
+        <v>3438</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>2661</v>
+        <v>2578</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -5576,12 +5496,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>CCBKNWE7</t>
+          <t>CCBKNWE12</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>4-7W Constant Current LED Driver, 300mA IP20 Rated Constant Current LED Driver Transformer, Converts AC85-265V into DC12-26V, IP20 Constant Current DC Transformers</t>
+          <t>12W</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -5590,29 +5510,29 @@
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>226.88</v>
+        <v>284.91</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>260</v>
+        <v>551</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>205</v>
+        <v>424</v>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>Sufficient stock</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5556,7 @@
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>0</v>
@@ -5645,16 +5565,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>629.04</v>
+        <v>670.7</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>475</v>
+        <v>430</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -5697,10 +5617,10 @@
         <v>178.37</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
@@ -5714,12 +5634,12 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>12IP6730</t>
+          <t>12IP6736</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>30W</t>
+          <t>36W</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -5731,26 +5651,26 @@
         <v>0</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>359.06</v>
+        <v>400.84</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>70</v>
+        <v>355</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>70</v>
+        <v>355</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>Maintain stock</t>
+          <t>Sufficient stock</t>
         </is>
       </c>
     </row>
@@ -5760,43 +5680,43 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>CRSF100BM</t>
+          <t>12IP6730</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>3.9 Inch Black Ceiling Canopy Kit Ceiling Plate, Modern Steel Canopy Kit Light Fixture for endant Light and Chandelier with All Hardware Includes Loop, Cross Bar and Mounting Screws.</t>
+          <t>30W</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Ceiling Rose</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>175.79</v>
+        <v>359.06</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>3990</v>
+        <v>70</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>3990</v>
+        <v>70</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Maintain stock</t>
         </is>
       </c>
     </row>
@@ -5806,43 +5726,43 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ENC8459</t>
+          <t>CRSF100BM</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Grün / Ja</t>
+          <t>3.9 Inch Black Ceiling Canopy Kit Ceiling Plate, Modern Steel Canopy Kit Light Fixture for endant Light and Chandelier with All Hardware Includes Loop, Cross Bar and Mounting Screws.</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Uncategorised</t>
+          <t>Ceiling Rose</t>
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>506.5</v>
+        <v>175.79</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>8</v>
+        <v>3972</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>10</v>
+        <v>3972</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>Restock soon</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -5852,43 +5772,43 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>5IP2050</t>
+          <t>ENC8459</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>50W</t>
+          <t>Grün / Ja</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>25</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>231</v>
+        <v>506.5</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>Sufficient stock</t>
+          <t>Restock soon</t>
         </is>
       </c>
     </row>
@@ -5927,10 +5847,10 @@
         <v>107.93</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -5944,43 +5864,43 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>LSDO300BI2PK+RPR44WH2PK</t>
+          <t>12IP67150</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>LEDSone Metall Lampenschirm Retro Industrielle Deckenbeleuchtung Pendelleuchte (Schwarz Innen Weiß, 2 Packung)</t>
+          <t>12V 150W IP67 Waterproof LED Driver Transformer For Outdoor Lighting</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Uncategorised</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>811.67</v>
+        <v>493.1</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>22</v>
+        <v>158</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>Restock soon</t>
+          <t>Sufficient stock</t>
         </is>
       </c>
     </row>
@@ -5990,12 +5910,12 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRYB+SCRN70BM+LSOL180BG</t>
+          <t>LSDO300BI2PK+RPR44WH2PK</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Combo Default Title.</t>
+          <t>LEDSone Metall Lampenschirm Retro Industrielle Deckenbeleuchtung Pendelleuchte (Schwarz Innen Weiß, 2 Packung)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -6004,10 +5924,10 @@
         </is>
       </c>
       <c r="E18" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="F18" s="8" t="n">
         <v>0</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>23</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>0</v>
@@ -6016,17 +5936,17 @@
         <v>23</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>455.4</v>
+        <v>811.67</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>Sufficient stock</t>
+          <t>Restock soon</t>
         </is>
       </c>
     </row>
@@ -6036,39 +5956,39 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>12BO48</t>
+          <t>CRSF100BM+PHSH1PBRYB+SCRN70BM+LSOL180BG</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>LED 48W Power Adapter Driver DC12V LED Transformer for LED Strips/MR16/CCTV</t>
+          <t>Combo Default Title.</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>234.85</v>
+        <v>455.4</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
@@ -6154,13 +6074,13 @@
         <v>22</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>467.79</v>
+        <v>467.44</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
@@ -6169,94 +6089,94 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>12IP67150</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>12V 150W IP67 Waterproof LED Driver Transformer For Outdoor Lighting</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Transformer</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="n">
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>LSCP150WH2PK+RPR44WH2PK</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>2Pack Metal Lamp Shades, 15cm White Light Shade, Modern Lampshades for Ceiling Lights, Easy Fit Pendant Light Shades Ceiling for Living Room, Bedroom, Kitchen, Hallway</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Lampshade</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="F22" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="H22" s="8" t="n">
+      <c r="G22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16" t="n">
         <v>22</v>
       </c>
-      <c r="I22" s="9" t="n">
-        <v>466.82</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>126</v>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>172</v>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>Sufficient stock</t>
+      <c r="I22" s="17" t="n">
+        <v>456.62</v>
+      </c>
+      <c r="J22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="15" t="inlineStr">
+        <is>
+          <t>Restock immediately</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>LSCP150WH2PK+RPR44WH2PK</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>2Pack Metal Lamp Shades, 15cm White Light Shade, Modern Lampshades for Ceiling Lights, Easy Fit Pendant Light Shades Ceiling for Living Room, Bedroom, Kitchen, Hallway</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>Lampshade</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="n">
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290GY</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>LEDSone Industrial Pendant Light Retro Chandelier Ceiling Light Vintage Lamp Ceiling Lighting Metal Shade for Restaurant Living Room Bedroom Kitchen Hallway Bar (Grigio)</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Uncategorised</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="16" t="n">
+      <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="16" t="n">
+      <c r="H23" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I23" s="17" t="n">
-        <v>456.62</v>
-      </c>
-      <c r="J23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="15" t="inlineStr">
-        <is>
-          <t>Restock immediately</t>
+      <c r="I23" s="13" t="n">
+        <v>434.13</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>369</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>503</v>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -6266,12 +6186,12 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290GY</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290BM</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>LEDSone Industrial Pendant Light Retro Chandelier Ceiling Light Vintage Lamp Ceiling Lighting Metal Shade for Restaurant Living Room Bedroom Kitchen Hallway Bar (Grigio)</t>
+          <t>Lámpara colgante industrial retro, lámpara de techo, lámpara vintage, iluminación de techo, pantalla de metal para (Negro, Sin bombilla)</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -6280,25 +6200,25 @@
         </is>
       </c>
       <c r="E24" s="8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F24" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>434.13</v>
+        <v>407.87</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -6312,43 +6232,43 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290BM</t>
+          <t>5IP2050</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Lámpara colgante industrial retro, lámpara de techo, lámpara vintage, iluminación de techo, pantalla de metal para (Negro, Sin bombilla)</t>
+          <t>50W</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Uncategorised</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>427.44</v>
+        <v>191.08</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>372</v>
+        <v>131</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>507</v>
+        <v>187</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Sufficient stock</t>
         </is>
       </c>
     </row>
@@ -6358,43 +6278,43 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>12IP6736</t>
+          <t>CNP1000YB</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>36W</t>
+          <t>LEDSone Heavy Chandelier Copper Light Chain 32mm x 17mm for Lighting Ceiling Lights Pendant Hanging Chain (Yellow Brass)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Small Categories</t>
         </is>
       </c>
       <c r="E26" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>21</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>284.93</v>
+        <v>105.15</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>355</v>
+        <v>139</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>507</v>
+        <v>199</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>Overstocked – review</t>
+          <t>Sufficient stock</t>
         </is>
       </c>
     </row>
@@ -6404,43 +6324,43 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>CNP1000YB</t>
+          <t>CRSF100BM+PHCH1BMRBM+LSCY290BM</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>LEDSone Heavy Chandelier Copper Light Chain 32mm x 17mm for Lighting Ceiling Lights Pendant Hanging Chain (Yellow Brass)</t>
+          <t>LEDSone Lámpara colgante de techo estilo retro industrial vintage con pantallas de cúpula curvada en color naranja, soporte E27 (Negro)</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Small Categories</t>
+          <t>Special-pr</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G27" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="H27" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="I27" s="13" t="n">
-        <v>105.15</v>
+        <v>394.01</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>139</v>
+        <v>369</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>199</v>
+        <v>554</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>Sufficient stock</t>
+          <t>Overstocked – review</t>
         </is>
       </c>
     </row>
@@ -6450,39 +6370,35 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHCH1BMRBM+LSCY290BM</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>LEDSone Lámpara colgante de techo estilo retro industrial vintage con pantallas de cúpula curvada en color naranja, soporte E27 (Negro)</t>
-        </is>
-      </c>
+          <t>LDMG95E274</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Special-pr</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="E28" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>20</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>394.01</v>
+        <v>107.68</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>372</v>
+        <v>917</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>558</v>
+        <v>1376</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
